--- a/artfynd/A 16235-2022 artfynd.xlsx
+++ b/artfynd/A 16235-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16235-2022 artfynd.xlsx
+++ b/artfynd/A 16235-2022 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>122744679</v>
       </c>
       <c r="B4" t="n">
-        <v>90960</v>
+        <v>90964</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 16235-2022 artfynd.xlsx
+++ b/artfynd/A 16235-2022 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>122744679</v>
       </c>
       <c r="B4" t="n">
-        <v>90964</v>
+        <v>90972</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 16235-2022 artfynd.xlsx
+++ b/artfynd/A 16235-2022 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>122744679</v>
       </c>
       <c r="B4" t="n">
-        <v>90972</v>
+        <v>90975</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester, Helene Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 16235-2022 artfynd.xlsx
+++ b/artfynd/A 16235-2022 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>122744679</v>
       </c>
       <c r="B4" t="n">
-        <v>90975</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristofer Wester, Helene Andersson</t>
+          <t>Helene Andersson, Kristofer Wester</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 16235-2022 artfynd.xlsx
+++ b/artfynd/A 16235-2022 artfynd.xlsx
@@ -911,12 +911,7 @@
         <v>122744679</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,12 +998,12 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 16235-2022 artfynd.xlsx
+++ b/artfynd/A 16235-2022 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>122744679</v>
       </c>
       <c r="B4" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16235-2022 artfynd.xlsx
+++ b/artfynd/A 16235-2022 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>122744679</v>
       </c>
       <c r="B4" t="n">
-        <v>91913</v>
+        <v>91919</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16235-2022 artfynd.xlsx
+++ b/artfynd/A 16235-2022 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>122744679</v>
       </c>
       <c r="B4" t="n">
-        <v>91919</v>
+        <v>91929</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16235-2022 artfynd.xlsx
+++ b/artfynd/A 16235-2022 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>122744679</v>
       </c>
       <c r="B4" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16235-2022 artfynd.xlsx
+++ b/artfynd/A 16235-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96221</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122744679</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,8 +991,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55959723</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>